--- a/hardware-carrier/production/BOM.xlsx
+++ b/hardware-carrier/production/BOM.xlsx
@@ -434,7 +434,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
@@ -737,39 +737,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Octal buffer 74HCT541, PDIP-20, 300 mil</t>
+          <t>Octal buffer 74HCT541, SO-20 300 mil (SOIC-20W land)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>SN74HCT541N</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>marketplace</t>
-        </is>
+          <t>74HCT541D,653</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>C547781</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>16712</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://shop.schukat.com/Texas-Instruments/SN74HCT541N/p/37554</t>
+          <t>https://www.lcsc.com/product-detail/Buffers-Drivers_Nexperia_C547781.html</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>AHCT or HCT, both have TTL input thresholds (VIH 2.0 V) and therefore switch reliably from the 3.3 V of the ESP32. The only difference is propagation delay, roughly 6 against 14 ns, irrelevant at 1250 ns per WS281x bit. LCSC does not stock the AHCT part in DIP, hence the marketplace sources. Which other types work and which do not is below.</t>
+          <t>Two things decide this part, and neither is the number 541.
+1) The T. HCT, AHCT and ACT have TTL input thresholds (VIH 2.0 V), so 3.3 V from the S3 switches them reliably on a 5 V supply. HC, AHC and AC do not: their threshold is 0.7 x VCC = 3.5 V.
+2) The package. The land is SOIC-20W: 1.27 mm pitch, rows 10.10 mm apart, copper from 3.63 to 6.47 mm off the axis, pads reaching 1.32 mm past the lead tip so an iron fits. Only the 1.27 mm parts land on it - TI calls that DW, Nexperia calls it D.
+Speed does not decide it: 14 ns against 6 ns is nothing next to a 1250 ns WS281x bit.</t>
         </is>
       </c>
     </row>
@@ -825,7 +830,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>The largest that fits the current placement: body 17.4 x 3.0 mm, 3.8 mm clear of the 1000uF can. Sits in the left and right hole (10.2 mm pitch). The MF-R900 (9 A, C208493) is the largest of the series but its body is 24.2 mm and would come within 0.40 mm of the can; both parts stand 20 to 25 mm tall. MF-RHT and MF-RG are 16 V parts above 1 A and unusable on 24 V.</t>
+          <t>The largest that fits the current placement: body 17.4 x 3.0 mm, 3.8 mm clear of the 1000uF can. Sits in the left and right hole (10.2 mm pitch). The MF-R900 (9 A, C208493) is the largest of the series but its body is 24.2 mm and would come within 0.40 mm of the can; both parts stand 20 to 25 mm tall. MF-RHT and MF-RG are 16 V parts above 1 A and unusable on 24 V.  Two numbers decide a replacement and neither is the current: the voltage (30 V, not 16) and the lead pitch (5.08 or 10.2 mm, nothing else). The table below is what has been checked so far.</t>
         </is>
       </c>
     </row>
@@ -1156,10 +1161,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -1202,127 +1207,127 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>lcsc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>330R bias+ / 330R bias- / 330R pixel</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SN74HCT541N, DIP-20, Texas</t>
+          <t>390R exists only in 0805 (C17655) and fits the 1206 land by hand if needed</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>approx. 1-2 EUR ea</t>
+          <t>0.004 USD</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/334274626871</t>
+          <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount-UniOhm_390R-3900-1_C17655.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>TVS bidir</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>5 x SN74HCT541N DIP-20</t>
+          <t>50 x SMF12CA, bidirectional, SOD-123FL</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>approx. 5-8 EUR / 5 pcs</t>
+          <t>approx. 8-10 EUR / 50 pcs</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/392631683671</t>
+          <t>https://www.amazon.com/Pcs-TVS-Diode-Bidirectional-Vrwm/dp/B0CNK4R5SC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>TVS bidir</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100 x SN74HCT541N DIP-20</t>
+          <t>SMF 200W SOD-123 TVS kit, 20 values x 10 pcs, bidirectional</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>volume price</t>
+          <t>approx. 15-20 EUR</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/235008609678</t>
+          <t>https://www.amazon.com/Values-SOD-123-Bi-Directional-Surface-Protection/dp/B0C5SLJQBB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>lcsc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>TVS bidir</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TI SN74HCT541N, DIP-20</t>
+          <t>Littelfuse SMF12CA, brand part, 1265 pcs</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>approx. 2-4 EUR ea</t>
+          <t>approx. 0.19 EUR ea</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/INSTRUMENTS-SN74HCT541N-INVERTING-BUFFER-DIP-20/dp/B00LQQBFTC</t>
+          <t>https://www.lcsc.com/product-detail/C1851360.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>distributor</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1330,142 +1335,142 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>12-24V -&gt; 5V buck</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Schukat SN74HCT541N</t>
+          <t>HiLetgo 5x MP1584EN Mini Buck</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>stocked</t>
+          <t>approx. 1.50 EUR ea</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://shop.schukat.com/Texas-Instruments/SN74HCT541N/p/37554</t>
+          <t>https://www.amazon.com/HiLetgo-MP1584EN-Adjustable-Module-Effect/dp/B00LTQU4EQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>lcsc</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>330R bias+ / 330R bias- / 330R pixel</t>
+          <t>12-24V -&gt; 5V buck</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>390R exists only in 0805 (C17655) and fits the 1206 land by hand if needed</t>
+          <t>Rakstore 4x MP1584 Step-Down</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.004 USD</t>
+          <t>approx. 1.50-2 EUR ea</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://lcsc.com/product-detail/Chip-Resistor-Surface-Mount-UniOhm_390R-3900-1_C17655.html</t>
+          <t>https://www.amazon.com/Rakstore-MP1584EN-Adjustable-Converter-Arduino/dp/B09J4KH116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TVS bidir</t>
+          <t>12-24V -&gt; 5V buck</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50 x SMF12CA, bidirectional, SOD-123FL</t>
+          <t>MP1584EN DC-DC Step Down 3A</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>approx. 8-10 EUR / 50 pcs</t>
+          <t>approx. 1-2 EUR</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Pcs-TVS-Diode-Bidirectional-Vrwm/dp/B0CNK4R5SC</t>
+          <t>https://www.ebay.com/itm/165434363045</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TVS bidir</t>
+          <t>12-24V -&gt; 5V buck</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SMF 200W SOD-123 TVS kit, 20 values x 10 pcs, bidirectional</t>
+          <t>MP1584EN 5/10 pcs adjustable</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>approx. 15-20 EUR</t>
+          <t>approx. 0.40-0.80 EUR ea</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Values-SOD-123-Bi-Directional-Surface-Protection/dp/B0C5SLJQBB</t>
+          <t>https://www.aliexpress.us/item/3256807294351325.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>lcsc</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TVS bidir</t>
+          <t>12-24V -&gt; 5V buck</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Littelfuse SMF12CA, brand part, 1265 pcs</t>
+          <t>MP1584 DC-DC 3A Buck, 10 pcs</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>approx. 0.19 EUR ea</t>
+          <t>approx. 0.50 EUR ea</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C1851360.html</t>
+          <t>https://www.aliexpress.us/item/3256803643955109.html</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1485,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12-24V -&gt; 5V buck</t>
+          <t>ESP32-S3 N16R8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>HiLetgo 5x MP1584EN Mini Buck</t>
+          <t>DIYmall 2x ESP32-S3-DevKitC-1 N16R8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>approx. 1.50 EUR ea</t>
+          <t>approx. 9-12 EUR ea</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/HiLetgo-MP1584EN-Adjustable-Module-Effect/dp/B00LTQU4EQ</t>
+          <t>https://www.amazon.com/DIYmall-ESP32-S3-DevKitC-1-N8R8-Development-ESP32-S3-WROOM-1-Module/dp/B0BSCXHB5S</t>
         </is>
       </c>
     </row>
@@ -1510,29 +1515,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12-24V -&gt; 5V buck</t>
+          <t>ESP32-S3 N16R8</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Rakstore 4x MP1584 Step-Down</t>
+          <t>YEJMKJ ESP32-S3-DevKitC-1-N16R8 Dual Type-C</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>approx. 1.50-2 EUR ea</t>
+          <t>approx. 10-14 EUR</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/Rakstore-MP1584EN-Adjustable-Converter-Arduino/dp/B09J4KH116</t>
+          <t>https://www.amazon.com/YEJMKJ-ESP32-S3-DevKitC-1-N16R8-Development-ESP32-S3-WROOM-1-Microcontroller/dp/B0CDRM6BGQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1540,22 +1545,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12-24V -&gt; 5V buck</t>
+          <t>ESP32-S3 N16R8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MP1584EN DC-DC Step Down 3A</t>
+          <t>3x ESP32-S3-DevKitC-1-N16R8, Dual Type-C</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>approx. 1-2 EUR</t>
+          <t>approx. 8-11 EUR ea</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/165434363045</t>
+          <t>https://www.amazon.com/ESP32-S3-DevKitC-1-N16R8-Development-Integrated-ESP32-S3-WROOM-1-Microcontroller/dp/B0DKF4DSQ4</t>
         </is>
       </c>
     </row>
@@ -1570,29 +1575,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12-24V -&gt; 5V buck</t>
+          <t>ESP32-S3 N16R8</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MP1584EN 5/10 pcs adjustable</t>
+          <t>ESP32-S3-DevKitC-1 N16R8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>approx. 0.40-0.80 EUR ea</t>
+          <t>approx. 6-9 EUR</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.us/item/3256807294351325.html</t>
+          <t>https://de.aliexpress.com/w/wholesale-ESP32-S3-DevKitC-1-N16R8.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>aliexpress</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1600,22 +1605,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12-24V -&gt; 5V buck</t>
+          <t>ESP32-S3 N16R8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MP1584 DC-DC 3A Buck, 10 pcs</t>
+          <t>ESP32-S3 DevKitC-1 N16R8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>approx. 0.50 EUR ea</t>
+          <t>approx. 8-13 EUR</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.us/item/3256803643955109.html</t>
+          <t>https://www.ebay.de/sch/i.html?_nkw=ESP32-S3+DevKitC-1+N16R8</t>
         </is>
       </c>
     </row>
@@ -1626,26 +1631,26 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8</t>
+          <t>MAX3485 DMXn</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DIYmall 2x ESP32-S3-DevKitC-1 N16R8</t>
+          <t>MusRock 5x MAX3485 TTL-RS485</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>approx. 9-12 EUR ea</t>
+          <t>approx. 2-3 EUR ea</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/DIYmall-ESP32-S3-DevKitC-1-N8R8-Development-ESP32-S3-WROOM-1-Module/dp/B0BSCXHB5S</t>
+          <t>https://www.amazon.com/MusRock-MAX3485-Transceiver-Unidirectional-Compact/dp/B0FTFXT876</t>
         </is>
       </c>
     </row>
@@ -1656,123 +1661,123 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8</t>
+          <t>MAX3485 DMXn</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>YEJMKJ ESP32-S3-DevKitC-1-N16R8 Dual Type-C</t>
+          <t>MAX3485 module TTL zu RS485</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>approx. 10-14 EUR</t>
+          <t>approx. 3 EUR</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/YEJMKJ-ESP32-S3-DevKitC-1-N16R8-Development-ESP32-S3-WROOM-1-Microcontroller/dp/B0CDRM6BGQ</t>
+          <t>https://www.amazon.com/MAX3485-Module-RS485-Development-Accessories/dp/B0DBGPC9B3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8</t>
+          <t>MAX3485 DMXn</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3x ESP32-S3-DevKitC-1-N16R8, Dual Type-C</t>
+          <t>5x MAX3485 TTL-RS485 3.0-3.6V</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>approx. 8-11 EUR ea</t>
+          <t>approx. 2 EUR ea</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/ESP32-S3-DevKitC-1-N16R8-Development-Integrated-ESP32-S3-WROOM-1-Microcontroller/dp/B0DKF4DSQ4</t>
+          <t>https://www.ebay.com/itm/225626333704</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>aliexpress</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8</t>
+          <t>MAX3485 DMXn</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3-DevKitC-1 N16R8</t>
+          <t>UART TTL zu RS485 Konverter 3.3V/5V</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>approx. 6-9 EUR</t>
+          <t>approx. 2-3 EUR</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://de.aliexpress.com/w/wholesale-ESP32-S3-DevKitC-1-N16R8.html</t>
+          <t>https://www.ebay.com/itm/122285209187</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 N16R8</t>
+          <t>MAX3485 DMXn</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ESP32-S3 DevKitC-1 N16R8</t>
+          <t>MAX3485 MAX485 RS485 Transceiver 3.3V/5V</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>approx. 8-13 EUR</t>
+          <t>approx. 0.80-1.50 EUR</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.de/sch/i.html?_nkw=ESP32-S3+DevKitC-1+N16R8</t>
+          <t>https://www.aliexpress.us/item/3256809536271896.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1785,17 +1790,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MusRock 5x MAX3485 TTL-RS485</t>
+          <t>MAX3485/MAX13487 TTL zu RS485</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>approx. 2-3 EUR ea</t>
+          <t>approx. 1-2 EUR</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/MusRock-MAX3485-Transceiver-Unidirectional-Compact/dp/B0FTFXT876</t>
+          <t>https://de.aliexpress.com/item/1005006007545162.html</t>
         </is>
       </c>
     </row>
@@ -1806,56 +1811,56 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 DMXn</t>
+          <t>OLED SDA/SCL/VCC/GND</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 module TTL zu RS485</t>
+          <t>1.3" OLED I2C SH1106 128x64</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>approx. 3 EUR</t>
+          <t>approx. 6-9 EUR</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/MAX3485-Module-RS485-Development-Accessories/dp/B0DBGPC9B3</t>
+          <t>https://www.amazon.de/s?k=1.3+inch+OLED+I2C+SH1106+128x64</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 DMXn</t>
+          <t>OLED SDA/SCL/VCC/GND</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5x MAX3485 TTL-RS485 3.0-3.6V</t>
+          <t>1.3 inch OLED SH1106 IIC</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>approx. 2 EUR ea</t>
+          <t>approx. 2-4 EUR</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/225626333704</t>
+          <t>https://de.aliexpress.com/w/wholesale-1.3-inch-OLED-SH1106-IIC.html</t>
         </is>
       </c>
     </row>
@@ -1866,93 +1871,93 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 DMXn</t>
+          <t>OLED SDA/SCL/VCC/GND</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>UART TTL zu RS485 Konverter 3.3V/5V</t>
+          <t>1.3 inch OLED SH1106 I2C</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>approx. 2-3 EUR</t>
+          <t>approx. 4-7 EUR</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/itm/122285209187</t>
+          <t>https://www.ebay.de/sch/i.html?_nkw=1.3+OLED+SH1106+I2C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>aliexpress</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 DMXn</t>
+          <t>USR-ES1 W5500</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 MAX485 RS485 Transceiver 3.3V/5V</t>
+          <t>TECNOIOT USR-ES1 W5500 (amazon.de)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>approx. 0.80-1.50 EUR</t>
+          <t>approx. 9-12 EUR</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.us/item/3256809536271896.html</t>
+          <t>https://www.amazon.de/USR-ES1-W5500-Chip-Ethernet-Converter/dp/B07RGLN436</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>aliexpress</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>MAX3485 DMXn</t>
+          <t>USR-ES1 W5500</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MAX3485/MAX13487 TTL zu RS485</t>
+          <t>DEVMO USR-ES1 W5500</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>approx. 1-2 EUR</t>
+          <t>approx. 8-11 EUR</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://de.aliexpress.com/item/1005006007545162.html</t>
+          <t>https://www.amazon.com/DEVMO-USR-ES1-W5500-Ethernet-Converter/dp/B07T4YHP7Q</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>aliexpress</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1960,22 +1965,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>OLED SDA/SCL/VCC/GND</t>
+          <t>USR-ES1 W5500</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1.3" OLED I2C SH1106 128x64</t>
+          <t>USR-ES1 W5500 SPI zu LAN</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>approx. 6-9 EUR</t>
+          <t>approx. 4-6 EUR</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/s?k=1.3+inch+OLED+I2C+SH1106+128x64</t>
+          <t>https://de.aliexpress.com/item/1005006061643080.html</t>
         </is>
       </c>
     </row>
@@ -1990,22 +1995,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>OLED SDA/SCL/VCC/GND</t>
+          <t>USR-ES1 W5500</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1.3 inch OLED SH1106 IIC</t>
+          <t>USR-ES1 W5500, 1-5 pcs</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>approx. 2-4 EUR</t>
+          <t>approx. 4-7 EUR</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://de.aliexpress.com/w/wholesale-1.3-inch-OLED-SH1106-IIC.html</t>
+          <t>https://de.aliexpress.com/item/1005001430749467.html</t>
         </is>
       </c>
     </row>
@@ -2020,170 +2025,20 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>OLED SDA/SCL/VCC/GND</t>
+          <t>USR-ES1 W5500</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1.3 inch OLED SH1106 I2C</t>
+          <t>USR-ES1 W5500 Ethernet module</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>approx. 4-7 EUR</t>
+          <t>approx. 6-9 EUR</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ebay.de/sch/i.html?_nkw=1.3+OLED+SH1106+I2C</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>TECNOIOT USR-ES1 W5500 (amazon.de)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>approx. 9-12 EUR</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/USR-ES1-W5500-Chip-Ethernet-Converter/dp/B07RGLN436</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>DEVMO USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>approx. 8-11 EUR</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/DEVMO-USR-ES1-W5500-Ethernet-Converter/dp/B07T4YHP7Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>aliexpress</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500 SPI zu LAN</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>approx. 4-6 EUR</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>https://de.aliexpress.com/item/1005006061643080.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>aliexpress</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500, 1-5 pcs</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>approx. 4-7 EUR</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>https://de.aliexpress.com/item/1005001430749467.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ebay</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>USR-ES1 W5500 Ethernet module</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>approx. 6-9 EUR</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>https://www.ebay.de/sch/i.html?_nkw=USR-ES1+W5500</t>
         </is>
@@ -2284,12 +2139,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>tme</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>mini blade fuse holder PCB mount ATO ATC</t>
+          <t>Keystone 3568 mini blade fuse holder</t>
         </is>
       </c>
     </row>
@@ -2301,12 +2156,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ebay</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PCB mount mini blade fuse holder 10.2mm</t>
+          <t>Keystone 3568 mini blade fuse holder PCB</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2173,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>aliexpress</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ATO mini blade fuse holder PCB through hole</t>
+          <t>mini blade fuse holder PCB vertical ATM</t>
         </is>
       </c>
     </row>
